--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106442</v>
+        <v>106456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106466</v>
+        <v>106597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106597</v>
+        <v>106598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106598</v>
+        <v>106599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3765-2026 artfynd.xlsx
+++ b/artfynd/A 3765-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377299</v>
       </c>
       <c r="B2" t="n">
-        <v>106614</v>
+        <v>106680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
